--- a/template/Template_perizinan Aset.xlsx
+++ b/template/Template_perizinan Aset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alvin\Documents\Coolyeah\PKT\Inventor\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B091A41-8E17-4C63-94AA-94C1B43EF53F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CE2C38-BB0B-4414-BBA7-3C3AFB05F099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -873,7 +873,7 @@
         <v>45658</v>
       </c>
       <c r="J2" s="3">
-        <v>46023</v>
+        <v>47119</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -905,7 +905,7 @@
         <v>45809</v>
       </c>
       <c r="J3" s="3">
-        <v>46174</v>
+        <v>47120</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -937,7 +937,7 @@
         <v>45658</v>
       </c>
       <c r="J4" s="3">
-        <v>46023</v>
+        <v>47121</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -969,7 +969,7 @@
         <v>45809</v>
       </c>
       <c r="J5" s="3">
-        <v>46174</v>
+        <v>47122</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1001,7 +1001,7 @@
         <v>45658</v>
       </c>
       <c r="J6" s="3">
-        <v>46023</v>
+        <v>47123</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1033,7 +1033,7 @@
         <v>45809</v>
       </c>
       <c r="J7" s="3">
-        <v>46174</v>
+        <v>47124</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1065,7 +1065,7 @@
         <v>45658</v>
       </c>
       <c r="J8" s="3">
-        <v>46023</v>
+        <v>47125</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1097,7 +1097,7 @@
         <v>45809</v>
       </c>
       <c r="J9" s="3">
-        <v>46174</v>
+        <v>47126</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1129,7 +1129,7 @@
         <v>45658</v>
       </c>
       <c r="J10" s="3">
-        <v>46023</v>
+        <v>47127</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1161,7 +1161,7 @@
         <v>45809</v>
       </c>
       <c r="J11" s="3">
-        <v>46174</v>
+        <v>47128</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1193,7 +1193,7 @@
         <v>45658</v>
       </c>
       <c r="J12" s="3">
-        <v>46023</v>
+        <v>47129</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1225,7 +1225,7 @@
         <v>45809</v>
       </c>
       <c r="J13" s="3">
-        <v>46174</v>
+        <v>47130</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1257,7 +1257,7 @@
         <v>45658</v>
       </c>
       <c r="J14" s="3">
-        <v>46023</v>
+        <v>47131</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1289,7 +1289,7 @@
         <v>45809</v>
       </c>
       <c r="J15" s="3">
-        <v>46174</v>
+        <v>47132</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1321,7 +1321,7 @@
         <v>45658</v>
       </c>
       <c r="J16" s="3">
-        <v>46023</v>
+        <v>47133</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1353,7 +1353,7 @@
         <v>45809</v>
       </c>
       <c r="J17" s="3">
-        <v>46174</v>
+        <v>47134</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1385,7 +1385,7 @@
         <v>45658</v>
       </c>
       <c r="J18" s="3">
-        <v>46023</v>
+        <v>47135</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1417,7 +1417,7 @@
         <v>45809</v>
       </c>
       <c r="J19" s="3">
-        <v>46174</v>
+        <v>47136</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1449,7 +1449,7 @@
         <v>45658</v>
       </c>
       <c r="J20" s="3">
-        <v>46023</v>
+        <v>47137</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1481,7 +1481,7 @@
         <v>45809</v>
       </c>
       <c r="J21" s="3">
-        <v>46174</v>
+        <v>47138</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1513,7 +1513,7 @@
         <v>45689</v>
       </c>
       <c r="J22" s="3">
-        <v>46054</v>
+        <v>47139</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1545,7 +1545,7 @@
         <v>45839</v>
       </c>
       <c r="J23" s="3">
-        <v>46204</v>
+        <v>47140</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1577,7 +1577,7 @@
         <v>45689</v>
       </c>
       <c r="J24" s="3">
-        <v>46054</v>
+        <v>47141</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1609,7 +1609,7 @@
         <v>45839</v>
       </c>
       <c r="J25" s="3">
-        <v>46204</v>
+        <v>47142</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1641,7 +1641,7 @@
         <v>45689</v>
       </c>
       <c r="J26" s="3">
-        <v>46054</v>
+        <v>47143</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -1673,7 +1673,7 @@
         <v>45839</v>
       </c>
       <c r="J27" s="3">
-        <v>46204</v>
+        <v>47144</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -1705,7 +1705,7 @@
         <v>45689</v>
       </c>
       <c r="J28" s="3">
-        <v>46054</v>
+        <v>47145</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -1737,7 +1737,7 @@
         <v>45839</v>
       </c>
       <c r="J29" s="3">
-        <v>46204</v>
+        <v>47146</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -1769,7 +1769,7 @@
         <v>45689</v>
       </c>
       <c r="J30" s="3">
-        <v>46054</v>
+        <v>47147</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -1801,7 +1801,7 @@
         <v>45839</v>
       </c>
       <c r="J31" s="3">
-        <v>46204</v>
+        <v>47148</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -1833,7 +1833,7 @@
         <v>45689</v>
       </c>
       <c r="J32" s="3">
-        <v>46054</v>
+        <v>47149</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -1865,7 +1865,7 @@
         <v>45839</v>
       </c>
       <c r="J33" s="3">
-        <v>46204</v>
+        <v>47150</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -1897,7 +1897,7 @@
         <v>45689</v>
       </c>
       <c r="J34" s="3">
-        <v>46054</v>
+        <v>47151</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -1929,7 +1929,7 @@
         <v>45839</v>
       </c>
       <c r="J35" s="3">
-        <v>46204</v>
+        <v>47152</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -1961,7 +1961,7 @@
         <v>45689</v>
       </c>
       <c r="J36" s="3">
-        <v>46054</v>
+        <v>47153</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -1993,7 +1993,7 @@
         <v>45839</v>
       </c>
       <c r="J37" s="3">
-        <v>46204</v>
+        <v>47154</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -2025,7 +2025,7 @@
         <v>45689</v>
       </c>
       <c r="J38" s="3">
-        <v>46054</v>
+        <v>47155</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -2057,7 +2057,7 @@
         <v>45839</v>
       </c>
       <c r="J39" s="3">
-        <v>46204</v>
+        <v>47156</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -2089,7 +2089,7 @@
         <v>45689</v>
       </c>
       <c r="J40" s="3">
-        <v>46054</v>
+        <v>47157</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -2121,7 +2121,7 @@
         <v>45839</v>
       </c>
       <c r="J41" s="3">
-        <v>46204</v>
+        <v>47158</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -2153,7 +2153,7 @@
         <v>45717</v>
       </c>
       <c r="J42" s="3">
-        <v>46082</v>
+        <v>47159</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -2185,7 +2185,7 @@
         <v>45870</v>
       </c>
       <c r="J43" s="3">
-        <v>46235</v>
+        <v>47160</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -2217,7 +2217,7 @@
         <v>45717</v>
       </c>
       <c r="J44" s="3">
-        <v>46082</v>
+        <v>47161</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -2249,7 +2249,7 @@
         <v>45870</v>
       </c>
       <c r="J45" s="3">
-        <v>46235</v>
+        <v>47162</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -2281,7 +2281,7 @@
         <v>45717</v>
       </c>
       <c r="J46" s="3">
-        <v>46082</v>
+        <v>47163</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -2313,7 +2313,7 @@
         <v>45870</v>
       </c>
       <c r="J47" s="3">
-        <v>46235</v>
+        <v>47164</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -2345,7 +2345,7 @@
         <v>45717</v>
       </c>
       <c r="J48" s="3">
-        <v>46082</v>
+        <v>47165</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -2377,7 +2377,7 @@
         <v>45870</v>
       </c>
       <c r="J49" s="3">
-        <v>46235</v>
+        <v>47166</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -2409,7 +2409,7 @@
         <v>45717</v>
       </c>
       <c r="J50" s="3">
-        <v>46082</v>
+        <v>47167</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -2441,7 +2441,7 @@
         <v>45870</v>
       </c>
       <c r="J51" s="3">
-        <v>46235</v>
+        <v>47168</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -2473,7 +2473,7 @@
         <v>45717</v>
       </c>
       <c r="J52" s="3">
-        <v>46082</v>
+        <v>47169</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -2505,7 +2505,7 @@
         <v>45870</v>
       </c>
       <c r="J53" s="3">
-        <v>46235</v>
+        <v>47170</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -2537,7 +2537,7 @@
         <v>45717</v>
       </c>
       <c r="J54" s="3">
-        <v>46082</v>
+        <v>47171</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -2569,7 +2569,7 @@
         <v>45870</v>
       </c>
       <c r="J55" s="3">
-        <v>46235</v>
+        <v>47172</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -2601,7 +2601,7 @@
         <v>45717</v>
       </c>
       <c r="J56" s="3">
-        <v>46082</v>
+        <v>47173</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -2633,7 +2633,7 @@
         <v>45870</v>
       </c>
       <c r="J57" s="3">
-        <v>46235</v>
+        <v>47174</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -2665,7 +2665,7 @@
         <v>45717</v>
       </c>
       <c r="J58" s="3">
-        <v>46082</v>
+        <v>47175</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -2697,7 +2697,7 @@
         <v>45870</v>
       </c>
       <c r="J59" s="3">
-        <v>46235</v>
+        <v>47176</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -2729,7 +2729,7 @@
         <v>45717</v>
       </c>
       <c r="J60" s="3">
-        <v>46082</v>
+        <v>47177</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
@@ -2761,7 +2761,7 @@
         <v>45870</v>
       </c>
       <c r="J61" s="3">
-        <v>46235</v>
+        <v>47178</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">

--- a/template/Template_perizinan Aset.xlsx
+++ b/template/Template_perizinan Aset.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alvin\Documents\Coolyeah\PKT\Inventor\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CE2C38-BB0B-4414-BBA7-3C3AFB05F099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C368154F-B5EE-42A5-A05A-84CE5C4D7226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="perizinan aset" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="83">
   <si>
     <t>Penanggung Jawab</t>
   </si>
@@ -28,15 +29,6 @@
     <t>Aktif</t>
   </si>
   <si>
-    <t>Overhead Crane 10 Ton</t>
-  </si>
-  <si>
-    <t>Bay 2</t>
-  </si>
-  <si>
-    <t>Bay 1</t>
-  </si>
-  <si>
     <t>Nama Aset / Master (Wajib)</t>
   </si>
   <si>
@@ -55,471 +47,12 @@
     <t>Tgl Expired</t>
   </si>
   <si>
-    <t>Overhead Crane 1 Ton</t>
-  </si>
-  <si>
-    <t>Aset Peralatan</t>
-  </si>
-  <si>
-    <t>CR-001</t>
-  </si>
-  <si>
     <t>Dept Pemeliharaan</t>
   </si>
   <si>
-    <t>Sertifikat Layak Operasi</t>
-  </si>
-  <si>
-    <t>SLO-CR001</t>
-  </si>
-  <si>
-    <t>Sertifikat K3</t>
-  </si>
-  <si>
-    <t>K3-CR001</t>
-  </si>
-  <si>
-    <t>Overhead Crane 2 Ton</t>
-  </si>
-  <si>
-    <t>CR-002</t>
-  </si>
-  <si>
-    <t>SLO-CR002</t>
-  </si>
-  <si>
-    <t>K3-CR002</t>
-  </si>
-  <si>
-    <t>Overhead Crane 3 Ton</t>
-  </si>
-  <si>
-    <t>CR-003</t>
-  </si>
-  <si>
-    <t>Bay 3</t>
-  </si>
-  <si>
-    <t>SLO-CR003</t>
-  </si>
-  <si>
-    <t>K3-CR003</t>
-  </si>
-  <si>
-    <t>Overhead Crane 4 Ton</t>
-  </si>
-  <si>
-    <t>CR-004</t>
-  </si>
-  <si>
-    <t>Bay 4</t>
-  </si>
-  <si>
-    <t>SLO-CR004</t>
-  </si>
-  <si>
-    <t>K3-CR004</t>
-  </si>
-  <si>
-    <t>Overhead Crane 5 Ton</t>
-  </si>
-  <si>
-    <t>CR-005</t>
-  </si>
-  <si>
-    <t>Bay 5</t>
-  </si>
-  <si>
-    <t>SLO-CR005</t>
-  </si>
-  <si>
-    <t>K3-CR005</t>
-  </si>
-  <si>
-    <t>Overhead Crane 6 Ton</t>
-  </si>
-  <si>
-    <t>CR-006</t>
-  </si>
-  <si>
-    <t>Bay 6</t>
-  </si>
-  <si>
-    <t>SLO-CR006</t>
-  </si>
-  <si>
-    <t>K3-CR006</t>
-  </si>
-  <si>
-    <t>Overhead Crane 7 Ton</t>
-  </si>
-  <si>
-    <t>CR-007</t>
-  </si>
-  <si>
-    <t>Bay 7</t>
-  </si>
-  <si>
-    <t>SLO-CR007</t>
-  </si>
-  <si>
-    <t>K3-CR007</t>
-  </si>
-  <si>
-    <t>Overhead Crane 8 Ton</t>
-  </si>
-  <si>
-    <t>CR-008</t>
-  </si>
-  <si>
-    <t>Bay 8</t>
-  </si>
-  <si>
-    <t>SLO-CR008</t>
-  </si>
-  <si>
-    <t>K3-CR008</t>
-  </si>
-  <si>
-    <t>Overhead Crane 9 Ton</t>
-  </si>
-  <si>
-    <t>CR-009</t>
-  </si>
-  <si>
-    <t>Bay 9</t>
-  </si>
-  <si>
-    <t>SLO-CR009</t>
-  </si>
-  <si>
-    <t>K3-CR009</t>
-  </si>
-  <si>
-    <t>CR-010</t>
-  </si>
-  <si>
-    <t>Bay 10</t>
-  </si>
-  <si>
-    <t>SLO-CR010</t>
-  </si>
-  <si>
-    <t>K3-CR010</t>
-  </si>
-  <si>
-    <t>Forklift 1 Ton</t>
-  </si>
-  <si>
-    <t>Aset Kendaraan</t>
-  </si>
-  <si>
-    <t>FL-001</t>
-  </si>
-  <si>
-    <t>Gudang 1</t>
-  </si>
-  <si>
     <t>Dept Logistik</t>
   </si>
   <si>
-    <t>SLO-FL001</t>
-  </si>
-  <si>
-    <t>K3-FL001</t>
-  </si>
-  <si>
-    <t>Forklift 2 Ton</t>
-  </si>
-  <si>
-    <t>FL-002</t>
-  </si>
-  <si>
-    <t>Gudang 2</t>
-  </si>
-  <si>
-    <t>SLO-FL002</t>
-  </si>
-  <si>
-    <t>K3-FL002</t>
-  </si>
-  <si>
-    <t>Forklift 3 Ton</t>
-  </si>
-  <si>
-    <t>FL-003</t>
-  </si>
-  <si>
-    <t>Gudang 3</t>
-  </si>
-  <si>
-    <t>SLO-FL003</t>
-  </si>
-  <si>
-    <t>K3-FL003</t>
-  </si>
-  <si>
-    <t>Forklift 4 Ton</t>
-  </si>
-  <si>
-    <t>FL-004</t>
-  </si>
-  <si>
-    <t>Gudang 4</t>
-  </si>
-  <si>
-    <t>SLO-FL004</t>
-  </si>
-  <si>
-    <t>K3-FL004</t>
-  </si>
-  <si>
-    <t>Forklift 5 Ton</t>
-  </si>
-  <si>
-    <t>FL-005</t>
-  </si>
-  <si>
-    <t>Gudang 5</t>
-  </si>
-  <si>
-    <t>SLO-FL005</t>
-  </si>
-  <si>
-    <t>K3-FL005</t>
-  </si>
-  <si>
-    <t>Forklift 6 Ton</t>
-  </si>
-  <si>
-    <t>FL-006</t>
-  </si>
-  <si>
-    <t>Gudang 6</t>
-  </si>
-  <si>
-    <t>SLO-FL006</t>
-  </si>
-  <si>
-    <t>K3-FL006</t>
-  </si>
-  <si>
-    <t>Forklift 7 Ton</t>
-  </si>
-  <si>
-    <t>FL-007</t>
-  </si>
-  <si>
-    <t>Gudang 7</t>
-  </si>
-  <si>
-    <t>SLO-FL007</t>
-  </si>
-  <si>
-    <t>K3-FL007</t>
-  </si>
-  <si>
-    <t>Forklift 8 Ton</t>
-  </si>
-  <si>
-    <t>FL-008</t>
-  </si>
-  <si>
-    <t>Gudang 8</t>
-  </si>
-  <si>
-    <t>SLO-FL008</t>
-  </si>
-  <si>
-    <t>K3-FL008</t>
-  </si>
-  <si>
-    <t>Forklift 9 Ton</t>
-  </si>
-  <si>
-    <t>FL-009</t>
-  </si>
-  <si>
-    <t>Gudang 9</t>
-  </si>
-  <si>
-    <t>SLO-FL009</t>
-  </si>
-  <si>
-    <t>K3-FL009</t>
-  </si>
-  <si>
-    <t>Forklift 10 Ton</t>
-  </si>
-  <si>
-    <t>FL-010</t>
-  </si>
-  <si>
-    <t>Gudang 10</t>
-  </si>
-  <si>
-    <t>SLO-FL010</t>
-  </si>
-  <si>
-    <t>K3-FL010</t>
-  </si>
-  <si>
-    <t>Kompresor Nitrogen 1</t>
-  </si>
-  <si>
-    <t>Mesin Produksi</t>
-  </si>
-  <si>
-    <t>KP-001</t>
-  </si>
-  <si>
-    <t>Pabrik 1</t>
-  </si>
-  <si>
-    <t>Dept Produksi</t>
-  </si>
-  <si>
-    <t>Sertifikat Tekanan Tinggi</t>
-  </si>
-  <si>
-    <t>STT-KP001</t>
-  </si>
-  <si>
-    <t>K3-KP001</t>
-  </si>
-  <si>
-    <t>KP-002</t>
-  </si>
-  <si>
-    <t>Pabrik 2</t>
-  </si>
-  <si>
-    <t>STT-KP002</t>
-  </si>
-  <si>
-    <t>K3-KP002</t>
-  </si>
-  <si>
-    <t>KP-003</t>
-  </si>
-  <si>
-    <t>Pabrik 3</t>
-  </si>
-  <si>
-    <t>STT-KP003</t>
-  </si>
-  <si>
-    <t>Kompresor Nitrogen 3</t>
-  </si>
-  <si>
-    <t>K3-KP003</t>
-  </si>
-  <si>
-    <t>Kompresor Nitrogen 4</t>
-  </si>
-  <si>
-    <t>KP-004</t>
-  </si>
-  <si>
-    <t>Pabrik 4</t>
-  </si>
-  <si>
-    <t>STT-KP004</t>
-  </si>
-  <si>
-    <t>K3-KP004</t>
-  </si>
-  <si>
-    <t>Kompresor Nitrogen 5</t>
-  </si>
-  <si>
-    <t>KP-005</t>
-  </si>
-  <si>
-    <t>Pabrik 5</t>
-  </si>
-  <si>
-    <t>STT-KP005</t>
-  </si>
-  <si>
-    <t>K3-KP005</t>
-  </si>
-  <si>
-    <t>Kompresor Nitrogen 6</t>
-  </si>
-  <si>
-    <t>KP-006</t>
-  </si>
-  <si>
-    <t>Pabrik 6</t>
-  </si>
-  <si>
-    <t>STT-KP006</t>
-  </si>
-  <si>
-    <t>K3-KP006</t>
-  </si>
-  <si>
-    <t>Kompresor Nitrogen 7</t>
-  </si>
-  <si>
-    <t>KP-007</t>
-  </si>
-  <si>
-    <t>Pabrik 7</t>
-  </si>
-  <si>
-    <t>STT-KP007</t>
-  </si>
-  <si>
-    <t>K3-KP007</t>
-  </si>
-  <si>
-    <t>Kompresor Nitrogen 8</t>
-  </si>
-  <si>
-    <t>KP-008</t>
-  </si>
-  <si>
-    <t>Pabrik 8</t>
-  </si>
-  <si>
-    <t>STT-KP008</t>
-  </si>
-  <si>
-    <t>K3-KP008</t>
-  </si>
-  <si>
-    <t>Kompresor Nitrogen 9</t>
-  </si>
-  <si>
-    <t>KP-009</t>
-  </si>
-  <si>
-    <t>Pabrik 9</t>
-  </si>
-  <si>
-    <t>STT-KP009</t>
-  </si>
-  <si>
-    <t>K3-KP009</t>
-  </si>
-  <si>
-    <t>Kompresor Nitrogen 10</t>
-  </si>
-  <si>
-    <t>KP-010</t>
-  </si>
-  <si>
-    <t>Pabrik 10</t>
-  </si>
-  <si>
-    <t>STT-KP010</t>
-  </si>
-  <si>
-    <t>K3-KP010</t>
-  </si>
-  <si>
     <t>Jenis Aset ( master )</t>
   </si>
   <si>
@@ -527,13 +60,223 @@
   </si>
   <si>
     <t>Lokasi aset</t>
+  </si>
+  <si>
+    <t>Jenis Aset (Master)</t>
+  </si>
+  <si>
+    <t>No Seri Aset</t>
+  </si>
+  <si>
+    <t>Lokasi Aset</t>
+  </si>
+  <si>
+    <t>Tanah Area Pabrik Utama</t>
+  </si>
+  <si>
+    <t>Tanah</t>
+  </si>
+  <si>
+    <t>TN-001</t>
+  </si>
+  <si>
+    <t>Kawasan Pabrik Utama</t>
+  </si>
+  <si>
+    <t>Dept Asset Management</t>
+  </si>
+  <si>
+    <t>Sertifikat Hak Guna Bangunan</t>
+  </si>
+  <si>
+    <t>HGB-TN001</t>
+  </si>
+  <si>
+    <t>Surat Ukur Tanah</t>
+  </si>
+  <si>
+    <t>SU-TN001</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Sertifikat Hak Pakai</t>
+  </si>
+  <si>
+    <t>HP-TN001</t>
+  </si>
+  <si>
+    <t>Tanah Area Gudang Logistik</t>
+  </si>
+  <si>
+    <t>TN-002</t>
+  </si>
+  <si>
+    <t>Kawasan Gudang</t>
+  </si>
+  <si>
+    <t>HGB-TN002</t>
+  </si>
+  <si>
+    <t>SU-TN002</t>
+  </si>
+  <si>
+    <t>Peta Bidang Tanah</t>
+  </si>
+  <si>
+    <t>PBT-TN002</t>
+  </si>
+  <si>
+    <t>Tanah Area Perkantoran</t>
+  </si>
+  <si>
+    <t>TN-003</t>
+  </si>
+  <si>
+    <t>Kawasan Perkantoran</t>
+  </si>
+  <si>
+    <t>Dept General Affair</t>
+  </si>
+  <si>
+    <t>HGB-TN003</t>
+  </si>
+  <si>
+    <t>SU-TN003</t>
+  </si>
+  <si>
+    <t>Tanah Area Workshop</t>
+  </si>
+  <si>
+    <t>TN-004</t>
+  </si>
+  <si>
+    <t>Area Workshop</t>
+  </si>
+  <si>
+    <t>HGB-TN004</t>
+  </si>
+  <si>
+    <t>Surat Keterangan Tanah</t>
+  </si>
+  <si>
+    <t>SKT-TN004</t>
+  </si>
+  <si>
+    <t>Tanah Area Terminal BBM</t>
+  </si>
+  <si>
+    <t>TN-005</t>
+  </si>
+  <si>
+    <t>Area Terminal BBM</t>
+  </si>
+  <si>
+    <t>Dept Operasional</t>
+  </si>
+  <si>
+    <t>HGB-TN005</t>
+  </si>
+  <si>
+    <t>SU-TN005</t>
+  </si>
+  <si>
+    <t>PBT-TN005</t>
+  </si>
+  <si>
+    <t>Tanah Area Parkir Kendaraan</t>
+  </si>
+  <si>
+    <t>TN-006</t>
+  </si>
+  <si>
+    <t>Area Parkir</t>
+  </si>
+  <si>
+    <t>HGB-TN006</t>
+  </si>
+  <si>
+    <t>SU-TN006</t>
+  </si>
+  <si>
+    <t>Tanah Area Utilitas Pabrik</t>
+  </si>
+  <si>
+    <t>TN-007</t>
+  </si>
+  <si>
+    <t>Area Utilitas</t>
+  </si>
+  <si>
+    <t>Dept Engineering</t>
+  </si>
+  <si>
+    <t>HP-TN007</t>
+  </si>
+  <si>
+    <t>SU-TN007</t>
+  </si>
+  <si>
+    <t>Tanah Area Ekspansi Pabrik</t>
+  </si>
+  <si>
+    <t>TN-008</t>
+  </si>
+  <si>
+    <t>Kawasan Ekspansi</t>
+  </si>
+  <si>
+    <t>Dept Project</t>
+  </si>
+  <si>
+    <t>HGB-TN008</t>
+  </si>
+  <si>
+    <t>HP-TN008</t>
+  </si>
+  <si>
+    <t>SU-TN008</t>
+  </si>
+  <si>
+    <t>Tanah Area Dermaga</t>
+  </si>
+  <si>
+    <t>TN-009</t>
+  </si>
+  <si>
+    <t>Kawasan Dermaga</t>
+  </si>
+  <si>
+    <t>HGB-TN009</t>
+  </si>
+  <si>
+    <t>SU-TN009</t>
+  </si>
+  <si>
+    <t>Tanah Area Fasilitas Umum</t>
+  </si>
+  <si>
+    <t>TN-010</t>
+  </si>
+  <si>
+    <t>Kawasan Fasilitas Umum</t>
+  </si>
+  <si>
+    <t>HP-TN010</t>
+  </si>
+  <si>
+    <t>SU-TN010</t>
+  </si>
+  <si>
+    <t>PBT-TN010</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -548,6 +291,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -572,13 +322,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -803,71 +562,71 @@
     <col min="1" max="1" width="43.6640625" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
     <col min="3" max="3" width="27.33203125" customWidth="1"/>
-    <col min="4" max="4" width="18.6640625" customWidth="1"/>
+    <col min="4" max="4" width="33" customWidth="1"/>
     <col min="5" max="5" width="26.44140625" customWidth="1"/>
     <col min="6" max="6" width="23.33203125" customWidth="1"/>
-    <col min="7" max="7" width="23.77734375" customWidth="1"/>
+    <col min="7" max="7" width="45.88671875" customWidth="1"/>
     <col min="8" max="8" width="75.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>166</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>167</v>
+        <v>11</v>
       </c>
       <c r="D1" t="s">
-        <v>168</v>
+        <v>12</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
       </c>
       <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" t="s">
-        <v>10</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="A2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
+      <c r="G2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="I2" s="3">
         <v>45658</v>
@@ -877,29 +636,29 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="A3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
+      <c r="G3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="I3" s="3">
         <v>45809</v>
@@ -909,29 +668,29 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="E4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="F4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" t="s">
-        <v>21</v>
+      <c r="G4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="I4" s="3">
         <v>45658</v>
@@ -941,29 +700,29 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="A5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" t="s">
-        <v>22</v>
+      <c r="G5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="I5" s="3">
         <v>45809</v>
@@ -973,29 +732,29 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" t="s">
-        <v>26</v>
+      <c r="H6" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="I6" s="3">
         <v>45658</v>
@@ -1005,29 +764,29 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="A7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" t="s">
-        <v>27</v>
+      <c r="G7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="I7" s="3">
         <v>45809</v>
@@ -1037,29 +796,29 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="A8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" t="s">
-        <v>31</v>
+      <c r="G8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="I8" s="3">
         <v>45658</v>
@@ -1069,29 +828,29 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="A9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" t="s">
-        <v>32</v>
+      <c r="G9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="I9" s="3">
         <v>45809</v>
@@ -1101,29 +860,29 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="A10" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" t="s">
-        <v>36</v>
+      <c r="G10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="I10" s="3">
         <v>45658</v>
@@ -1133,29 +892,29 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" t="s">
-        <v>37</v>
+      <c r="G11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="I11" s="3">
         <v>45809</v>
@@ -1165,29 +924,29 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="A12" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" t="s">
-        <v>41</v>
+      <c r="G12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="I12" s="3">
         <v>45658</v>
@@ -1197,29 +956,29 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="A13" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G13" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" t="s">
-        <v>42</v>
+      <c r="G13" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="I13" s="3">
         <v>45809</v>
@@ -1229,29 +988,29 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="A14" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" t="s">
-        <v>46</v>
+      <c r="G14" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="I14" s="3">
         <v>45658</v>
@@ -1261,29 +1020,29 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="A15" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G15" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" t="s">
-        <v>47</v>
+      <c r="G15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="I15" s="3">
         <v>45809</v>
@@ -1293,29 +1052,29 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="A16" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G16" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" t="s">
-        <v>51</v>
+      <c r="G16" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="I16" s="3">
         <v>45658</v>
@@ -1325,29 +1084,29 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="A17" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G17" t="s">
-        <v>17</v>
-      </c>
-      <c r="H17" t="s">
-        <v>52</v>
+      <c r="G17" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="I17" s="3">
         <v>45809</v>
@@ -1357,29 +1116,29 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" t="s">
-        <v>55</v>
-      </c>
-      <c r="E18" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="A18" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G18" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" t="s">
-        <v>56</v>
+      <c r="G18" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="I18" s="3">
         <v>45658</v>
@@ -1389,29 +1148,29 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" t="s">
-        <v>55</v>
-      </c>
-      <c r="E19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="A19" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G19" t="s">
-        <v>17</v>
-      </c>
-      <c r="H19" t="s">
-        <v>57</v>
+      <c r="G19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="I19" s="3">
         <v>45809</v>
@@ -1421,29 +1180,29 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>2</v>
-      </c>
-      <c r="B20" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" t="s">
-        <v>59</v>
-      </c>
-      <c r="E20" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="A20" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G20" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" t="s">
-        <v>60</v>
+      <c r="G20" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>70</v>
       </c>
       <c r="I20" s="3">
         <v>45658</v>
@@ -1453,29 +1212,29 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>2</v>
-      </c>
-      <c r="B21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="A21" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G21" t="s">
-        <v>17</v>
-      </c>
-      <c r="H21" t="s">
-        <v>61</v>
+      <c r="G21" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="I21" s="3">
         <v>45809</v>
@@ -1485,29 +1244,29 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>62</v>
-      </c>
-      <c r="B22" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" t="s">
-        <v>64</v>
-      </c>
-      <c r="D22" t="s">
-        <v>65</v>
-      </c>
-      <c r="E22" t="s">
-        <v>66</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="A22" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H22" t="s">
-        <v>67</v>
+      <c r="G22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="I22" s="3">
         <v>45689</v>
@@ -1517,29 +1276,29 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" t="s">
-        <v>64</v>
-      </c>
-      <c r="D23" t="s">
-        <v>65</v>
-      </c>
-      <c r="E23" t="s">
-        <v>66</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="A23" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F23" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G23" t="s">
-        <v>17</v>
-      </c>
-      <c r="H23" t="s">
-        <v>68</v>
+      <c r="G23" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="I23" s="3">
         <v>45839</v>
@@ -1549,29 +1308,29 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E24" t="s">
-        <v>66</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="A24" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G24" t="s">
-        <v>15</v>
-      </c>
-      <c r="H24" t="s">
-        <v>72</v>
+      <c r="G24" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>80</v>
       </c>
       <c r="I24" s="3">
         <v>45689</v>
@@ -1581,29 +1340,29 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>69</v>
-      </c>
-      <c r="B25" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" t="s">
-        <v>71</v>
-      </c>
-      <c r="E25" t="s">
-        <v>66</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="A25" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G25" t="s">
-        <v>17</v>
-      </c>
-      <c r="H25" t="s">
-        <v>73</v>
+      <c r="G25" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="I25" s="3">
         <v>45839</v>
@@ -1613,29 +1372,29 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>74</v>
-      </c>
-      <c r="B26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C26" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" t="s">
-        <v>76</v>
-      </c>
-      <c r="E26" t="s">
-        <v>66</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="A26" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G26" t="s">
-        <v>15</v>
-      </c>
-      <c r="H26" t="s">
-        <v>77</v>
+      <c r="G26" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="I26" s="3">
         <v>45689</v>
@@ -1645,30 +1404,6 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>74</v>
-      </c>
-      <c r="B27" t="s">
-        <v>63</v>
-      </c>
-      <c r="C27" t="s">
-        <v>75</v>
-      </c>
-      <c r="D27" t="s">
-        <v>76</v>
-      </c>
-      <c r="E27" t="s">
-        <v>66</v>
-      </c>
-      <c r="F27" t="s">
-        <v>1</v>
-      </c>
-      <c r="G27" t="s">
-        <v>17</v>
-      </c>
-      <c r="H27" t="s">
-        <v>78</v>
-      </c>
       <c r="I27" s="3">
         <v>45839</v>
       </c>
@@ -1677,1144 +1412,150 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>79</v>
-      </c>
-      <c r="B28" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" t="s">
-        <v>80</v>
-      </c>
-      <c r="D28" t="s">
-        <v>81</v>
-      </c>
-      <c r="E28" t="s">
-        <v>66</v>
-      </c>
-      <c r="F28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G28" t="s">
-        <v>15</v>
-      </c>
-      <c r="H28" t="s">
-        <v>82</v>
-      </c>
-      <c r="I28" s="3">
-        <v>45689</v>
-      </c>
-      <c r="J28" s="3">
-        <v>47145</v>
-      </c>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
     </row>
     <row r="29" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>79</v>
-      </c>
-      <c r="B29" t="s">
-        <v>63</v>
-      </c>
-      <c r="C29" t="s">
-        <v>80</v>
-      </c>
-      <c r="D29" t="s">
-        <v>81</v>
-      </c>
-      <c r="E29" t="s">
-        <v>66</v>
-      </c>
-      <c r="F29" t="s">
-        <v>1</v>
-      </c>
-      <c r="G29" t="s">
-        <v>17</v>
-      </c>
-      <c r="H29" t="s">
-        <v>83</v>
-      </c>
-      <c r="I29" s="3">
-        <v>45839</v>
-      </c>
-      <c r="J29" s="3">
-        <v>47146</v>
-      </c>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
     </row>
     <row r="30" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>84</v>
-      </c>
-      <c r="B30" t="s">
-        <v>63</v>
-      </c>
-      <c r="C30" t="s">
-        <v>85</v>
-      </c>
-      <c r="D30" t="s">
-        <v>86</v>
-      </c>
-      <c r="E30" t="s">
-        <v>66</v>
-      </c>
-      <c r="F30" t="s">
-        <v>1</v>
-      </c>
-      <c r="G30" t="s">
-        <v>15</v>
-      </c>
-      <c r="H30" t="s">
-        <v>87</v>
-      </c>
-      <c r="I30" s="3">
-        <v>45689</v>
-      </c>
-      <c r="J30" s="3">
-        <v>47147</v>
-      </c>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
     </row>
     <row r="31" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>84</v>
-      </c>
-      <c r="B31" t="s">
-        <v>63</v>
-      </c>
-      <c r="C31" t="s">
-        <v>85</v>
-      </c>
-      <c r="D31" t="s">
-        <v>86</v>
-      </c>
-      <c r="E31" t="s">
-        <v>66</v>
-      </c>
-      <c r="F31" t="s">
-        <v>1</v>
-      </c>
-      <c r="G31" t="s">
-        <v>17</v>
-      </c>
-      <c r="H31" t="s">
-        <v>88</v>
-      </c>
-      <c r="I31" s="3">
-        <v>45839</v>
-      </c>
-      <c r="J31" s="3">
-        <v>47148</v>
-      </c>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
     </row>
     <row r="32" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>89</v>
-      </c>
-      <c r="B32" t="s">
-        <v>63</v>
-      </c>
-      <c r="C32" t="s">
-        <v>90</v>
-      </c>
-      <c r="D32" t="s">
-        <v>91</v>
-      </c>
-      <c r="E32" t="s">
-        <v>66</v>
-      </c>
-      <c r="F32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H32" t="s">
-        <v>92</v>
-      </c>
-      <c r="I32" s="3">
-        <v>45689</v>
-      </c>
-      <c r="J32" s="3">
-        <v>47149</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>89</v>
-      </c>
-      <c r="B33" t="s">
-        <v>63</v>
-      </c>
-      <c r="C33" t="s">
-        <v>90</v>
-      </c>
-      <c r="D33" t="s">
-        <v>91</v>
-      </c>
-      <c r="E33" t="s">
-        <v>66</v>
-      </c>
-      <c r="F33" t="s">
-        <v>1</v>
-      </c>
-      <c r="G33" t="s">
-        <v>17</v>
-      </c>
-      <c r="H33" t="s">
-        <v>93</v>
-      </c>
-      <c r="I33" s="3">
-        <v>45839</v>
-      </c>
-      <c r="J33" s="3">
-        <v>47150</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>94</v>
-      </c>
-      <c r="B34" t="s">
-        <v>63</v>
-      </c>
-      <c r="C34" t="s">
-        <v>95</v>
-      </c>
-      <c r="D34" t="s">
-        <v>96</v>
-      </c>
-      <c r="E34" t="s">
-        <v>66</v>
-      </c>
-      <c r="F34" t="s">
-        <v>1</v>
-      </c>
-      <c r="G34" t="s">
-        <v>15</v>
-      </c>
-      <c r="H34" t="s">
-        <v>97</v>
-      </c>
-      <c r="I34" s="3">
-        <v>45689</v>
-      </c>
-      <c r="J34" s="3">
-        <v>47151</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>94</v>
-      </c>
-      <c r="B35" t="s">
-        <v>63</v>
-      </c>
-      <c r="C35" t="s">
-        <v>95</v>
-      </c>
-      <c r="D35" t="s">
-        <v>96</v>
-      </c>
-      <c r="E35" t="s">
-        <v>66</v>
-      </c>
-      <c r="F35" t="s">
-        <v>1</v>
-      </c>
-      <c r="G35" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" t="s">
-        <v>98</v>
-      </c>
-      <c r="I35" s="3">
-        <v>45839</v>
-      </c>
-      <c r="J35" s="3">
-        <v>47152</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>99</v>
-      </c>
-      <c r="B36" t="s">
-        <v>63</v>
-      </c>
-      <c r="C36" t="s">
-        <v>100</v>
-      </c>
-      <c r="D36" t="s">
-        <v>101</v>
-      </c>
-      <c r="E36" t="s">
-        <v>66</v>
-      </c>
-      <c r="F36" t="s">
-        <v>1</v>
-      </c>
-      <c r="G36" t="s">
-        <v>15</v>
-      </c>
-      <c r="H36" t="s">
-        <v>102</v>
-      </c>
-      <c r="I36" s="3">
-        <v>45689</v>
-      </c>
-      <c r="J36" s="3">
-        <v>47153</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>99</v>
-      </c>
-      <c r="B37" t="s">
-        <v>63</v>
-      </c>
-      <c r="C37" t="s">
-        <v>100</v>
-      </c>
-      <c r="D37" t="s">
-        <v>101</v>
-      </c>
-      <c r="E37" t="s">
-        <v>66</v>
-      </c>
-      <c r="F37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G37" t="s">
-        <v>17</v>
-      </c>
-      <c r="H37" t="s">
-        <v>103</v>
-      </c>
-      <c r="I37" s="3">
-        <v>45839</v>
-      </c>
-      <c r="J37" s="3">
-        <v>47154</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>104</v>
-      </c>
-      <c r="B38" t="s">
-        <v>63</v>
-      </c>
-      <c r="C38" t="s">
-        <v>105</v>
-      </c>
-      <c r="D38" t="s">
-        <v>106</v>
-      </c>
-      <c r="E38" t="s">
-        <v>66</v>
-      </c>
-      <c r="F38" t="s">
-        <v>1</v>
-      </c>
-      <c r="G38" t="s">
-        <v>15</v>
-      </c>
-      <c r="H38" t="s">
-        <v>107</v>
-      </c>
-      <c r="I38" s="3">
-        <v>45689</v>
-      </c>
-      <c r="J38" s="3">
-        <v>47155</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>104</v>
-      </c>
-      <c r="B39" t="s">
-        <v>63</v>
-      </c>
-      <c r="C39" t="s">
-        <v>105</v>
-      </c>
-      <c r="D39" t="s">
-        <v>106</v>
-      </c>
-      <c r="E39" t="s">
-        <v>66</v>
-      </c>
-      <c r="F39" t="s">
-        <v>1</v>
-      </c>
-      <c r="G39" t="s">
-        <v>17</v>
-      </c>
-      <c r="H39" t="s">
-        <v>108</v>
-      </c>
-      <c r="I39" s="3">
-        <v>45839</v>
-      </c>
-      <c r="J39" s="3">
-        <v>47156</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>109</v>
-      </c>
-      <c r="B40" t="s">
-        <v>63</v>
-      </c>
-      <c r="C40" t="s">
-        <v>110</v>
-      </c>
-      <c r="D40" t="s">
-        <v>111</v>
-      </c>
-      <c r="E40" t="s">
-        <v>66</v>
-      </c>
-      <c r="F40" t="s">
-        <v>1</v>
-      </c>
-      <c r="G40" t="s">
-        <v>15</v>
-      </c>
-      <c r="H40" t="s">
-        <v>112</v>
-      </c>
-      <c r="I40" s="3">
-        <v>45689</v>
-      </c>
-      <c r="J40" s="3">
-        <v>47157</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>109</v>
-      </c>
-      <c r="B41" t="s">
-        <v>63</v>
-      </c>
-      <c r="C41" t="s">
-        <v>110</v>
-      </c>
-      <c r="D41" t="s">
-        <v>111</v>
-      </c>
-      <c r="E41" t="s">
-        <v>66</v>
-      </c>
-      <c r="F41" t="s">
-        <v>1</v>
-      </c>
-      <c r="G41" t="s">
-        <v>17</v>
-      </c>
-      <c r="H41" t="s">
-        <v>113</v>
-      </c>
-      <c r="I41" s="3">
-        <v>45839</v>
-      </c>
-      <c r="J41" s="3">
-        <v>47158</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>114</v>
-      </c>
-      <c r="B42" t="s">
-        <v>115</v>
-      </c>
-      <c r="C42" t="s">
-        <v>116</v>
-      </c>
-      <c r="D42" t="s">
-        <v>117</v>
-      </c>
-      <c r="E42" t="s">
-        <v>118</v>
-      </c>
-      <c r="F42" t="s">
-        <v>1</v>
-      </c>
-      <c r="G42" t="s">
-        <v>119</v>
-      </c>
-      <c r="H42" t="s">
-        <v>120</v>
-      </c>
-      <c r="I42" s="3">
-        <v>45717</v>
-      </c>
-      <c r="J42" s="3">
-        <v>47159</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>114</v>
-      </c>
-      <c r="B43" t="s">
-        <v>115</v>
-      </c>
-      <c r="C43" t="s">
-        <v>116</v>
-      </c>
-      <c r="D43" t="s">
-        <v>117</v>
-      </c>
-      <c r="E43" t="s">
-        <v>118</v>
-      </c>
-      <c r="F43" t="s">
-        <v>1</v>
-      </c>
-      <c r="G43" t="s">
-        <v>17</v>
-      </c>
-      <c r="H43" t="s">
-        <v>121</v>
-      </c>
-      <c r="I43" s="3">
-        <v>45870</v>
-      </c>
-      <c r="J43" s="3">
-        <v>47160</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>114</v>
-      </c>
-      <c r="B44" t="s">
-        <v>115</v>
-      </c>
-      <c r="C44" t="s">
-        <v>122</v>
-      </c>
-      <c r="D44" t="s">
-        <v>123</v>
-      </c>
-      <c r="E44" t="s">
-        <v>118</v>
-      </c>
-      <c r="F44" t="s">
-        <v>1</v>
-      </c>
-      <c r="G44" t="s">
-        <v>119</v>
-      </c>
-      <c r="H44" t="s">
-        <v>124</v>
-      </c>
-      <c r="I44" s="3">
-        <v>45717</v>
-      </c>
-      <c r="J44" s="3">
-        <v>47161</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>114</v>
-      </c>
-      <c r="B45" t="s">
-        <v>115</v>
-      </c>
-      <c r="C45" t="s">
-        <v>122</v>
-      </c>
-      <c r="D45" t="s">
-        <v>123</v>
-      </c>
-      <c r="E45" t="s">
-        <v>118</v>
-      </c>
-      <c r="F45" t="s">
-        <v>1</v>
-      </c>
-      <c r="G45" t="s">
-        <v>17</v>
-      </c>
-      <c r="H45" t="s">
-        <v>125</v>
-      </c>
-      <c r="I45" s="3">
-        <v>45870</v>
-      </c>
-      <c r="J45" s="3">
-        <v>47162</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>114</v>
-      </c>
-      <c r="B46" t="s">
-        <v>115</v>
-      </c>
-      <c r="C46" t="s">
-        <v>126</v>
-      </c>
-      <c r="D46" t="s">
-        <v>127</v>
-      </c>
-      <c r="E46" t="s">
-        <v>118</v>
-      </c>
-      <c r="F46" t="s">
-        <v>1</v>
-      </c>
-      <c r="G46" t="s">
-        <v>119</v>
-      </c>
-      <c r="H46" t="s">
-        <v>128</v>
-      </c>
-      <c r="I46" s="3">
-        <v>45717</v>
-      </c>
-      <c r="J46" s="3">
-        <v>47163</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>129</v>
-      </c>
-      <c r="B47" t="s">
-        <v>115</v>
-      </c>
-      <c r="C47" t="s">
-        <v>126</v>
-      </c>
-      <c r="D47" t="s">
-        <v>127</v>
-      </c>
-      <c r="E47" t="s">
-        <v>118</v>
-      </c>
-      <c r="F47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G47" t="s">
-        <v>17</v>
-      </c>
-      <c r="H47" t="s">
-        <v>130</v>
-      </c>
-      <c r="I47" s="3">
-        <v>45870</v>
-      </c>
-      <c r="J47" s="3">
-        <v>47164</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>131</v>
-      </c>
-      <c r="B48" t="s">
-        <v>115</v>
-      </c>
-      <c r="C48" t="s">
-        <v>132</v>
-      </c>
-      <c r="D48" t="s">
-        <v>133</v>
-      </c>
-      <c r="E48" t="s">
-        <v>118</v>
-      </c>
-      <c r="F48" t="s">
-        <v>1</v>
-      </c>
-      <c r="G48" t="s">
-        <v>119</v>
-      </c>
-      <c r="H48" t="s">
-        <v>134</v>
-      </c>
-      <c r="I48" s="3">
-        <v>45717</v>
-      </c>
-      <c r="J48" s="3">
-        <v>47165</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>131</v>
-      </c>
-      <c r="B49" t="s">
-        <v>115</v>
-      </c>
-      <c r="C49" t="s">
-        <v>132</v>
-      </c>
-      <c r="D49" t="s">
-        <v>133</v>
-      </c>
-      <c r="E49" t="s">
-        <v>118</v>
-      </c>
-      <c r="F49" t="s">
-        <v>1</v>
-      </c>
-      <c r="G49" t="s">
-        <v>17</v>
-      </c>
-      <c r="H49" t="s">
-        <v>135</v>
-      </c>
-      <c r="I49" s="3">
-        <v>45870</v>
-      </c>
-      <c r="J49" s="3">
-        <v>47166</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>136</v>
-      </c>
-      <c r="B50" t="s">
-        <v>115</v>
-      </c>
-      <c r="C50" t="s">
-        <v>137</v>
-      </c>
-      <c r="D50" t="s">
-        <v>138</v>
-      </c>
-      <c r="E50" t="s">
-        <v>118</v>
-      </c>
-      <c r="F50" t="s">
-        <v>1</v>
-      </c>
-      <c r="G50" t="s">
-        <v>119</v>
-      </c>
-      <c r="H50" t="s">
-        <v>139</v>
-      </c>
-      <c r="I50" s="3">
-        <v>45717</v>
-      </c>
-      <c r="J50" s="3">
-        <v>47167</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>136</v>
-      </c>
-      <c r="B51" t="s">
-        <v>115</v>
-      </c>
-      <c r="C51" t="s">
-        <v>137</v>
-      </c>
-      <c r="D51" t="s">
-        <v>138</v>
-      </c>
-      <c r="E51" t="s">
-        <v>118</v>
-      </c>
-      <c r="F51" t="s">
-        <v>1</v>
-      </c>
-      <c r="G51" t="s">
-        <v>17</v>
-      </c>
-      <c r="H51" t="s">
-        <v>140</v>
-      </c>
-      <c r="I51" s="3">
-        <v>45870</v>
-      </c>
-      <c r="J51" s="3">
-        <v>47168</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>141</v>
-      </c>
-      <c r="B52" t="s">
-        <v>115</v>
-      </c>
-      <c r="C52" t="s">
-        <v>142</v>
-      </c>
-      <c r="D52" t="s">
-        <v>143</v>
-      </c>
-      <c r="E52" t="s">
-        <v>118</v>
-      </c>
-      <c r="F52" t="s">
-        <v>1</v>
-      </c>
-      <c r="G52" t="s">
-        <v>119</v>
-      </c>
-      <c r="H52" t="s">
-        <v>144</v>
-      </c>
-      <c r="I52" s="3">
-        <v>45717</v>
-      </c>
-      <c r="J52" s="3">
-        <v>47169</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>141</v>
-      </c>
-      <c r="B53" t="s">
-        <v>115</v>
-      </c>
-      <c r="C53" t="s">
-        <v>142</v>
-      </c>
-      <c r="D53" t="s">
-        <v>143</v>
-      </c>
-      <c r="E53" t="s">
-        <v>118</v>
-      </c>
-      <c r="F53" t="s">
-        <v>1</v>
-      </c>
-      <c r="G53" t="s">
-        <v>17</v>
-      </c>
-      <c r="H53" t="s">
-        <v>145</v>
-      </c>
-      <c r="I53" s="3">
-        <v>45870</v>
-      </c>
-      <c r="J53" s="3">
-        <v>47170</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>146</v>
-      </c>
-      <c r="B54" t="s">
-        <v>115</v>
-      </c>
-      <c r="C54" t="s">
-        <v>147</v>
-      </c>
-      <c r="D54" t="s">
-        <v>148</v>
-      </c>
-      <c r="E54" t="s">
-        <v>118</v>
-      </c>
-      <c r="F54" t="s">
-        <v>1</v>
-      </c>
-      <c r="G54" t="s">
-        <v>119</v>
-      </c>
-      <c r="H54" t="s">
-        <v>149</v>
-      </c>
-      <c r="I54" s="3">
-        <v>45717</v>
-      </c>
-      <c r="J54" s="3">
-        <v>47171</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>146</v>
-      </c>
-      <c r="B55" t="s">
-        <v>115</v>
-      </c>
-      <c r="C55" t="s">
-        <v>147</v>
-      </c>
-      <c r="D55" t="s">
-        <v>148</v>
-      </c>
-      <c r="E55" t="s">
-        <v>118</v>
-      </c>
-      <c r="F55" t="s">
-        <v>1</v>
-      </c>
-      <c r="G55" t="s">
-        <v>17</v>
-      </c>
-      <c r="H55" t="s">
-        <v>150</v>
-      </c>
-      <c r="I55" s="3">
-        <v>45870</v>
-      </c>
-      <c r="J55" s="3">
-        <v>47172</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>151</v>
-      </c>
-      <c r="B56" t="s">
-        <v>115</v>
-      </c>
-      <c r="C56" t="s">
-        <v>152</v>
-      </c>
-      <c r="D56" t="s">
-        <v>153</v>
-      </c>
-      <c r="E56" t="s">
-        <v>118</v>
-      </c>
-      <c r="F56" t="s">
-        <v>1</v>
-      </c>
-      <c r="G56" t="s">
-        <v>119</v>
-      </c>
-      <c r="H56" t="s">
-        <v>154</v>
-      </c>
-      <c r="I56" s="3">
-        <v>45717</v>
-      </c>
-      <c r="J56" s="3">
-        <v>47173</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>151</v>
-      </c>
-      <c r="B57" t="s">
-        <v>115</v>
-      </c>
-      <c r="C57" t="s">
-        <v>152</v>
-      </c>
-      <c r="D57" t="s">
-        <v>153</v>
-      </c>
-      <c r="E57" t="s">
-        <v>118</v>
-      </c>
-      <c r="F57" t="s">
-        <v>1</v>
-      </c>
-      <c r="G57" t="s">
-        <v>17</v>
-      </c>
-      <c r="H57" t="s">
-        <v>155</v>
-      </c>
-      <c r="I57" s="3">
-        <v>45870</v>
-      </c>
-      <c r="J57" s="3">
-        <v>47174</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>156</v>
-      </c>
-      <c r="B58" t="s">
-        <v>115</v>
-      </c>
-      <c r="C58" t="s">
-        <v>157</v>
-      </c>
-      <c r="D58" t="s">
-        <v>158</v>
-      </c>
-      <c r="E58" t="s">
-        <v>118</v>
-      </c>
-      <c r="F58" t="s">
-        <v>1</v>
-      </c>
-      <c r="G58" t="s">
-        <v>119</v>
-      </c>
-      <c r="H58" t="s">
-        <v>159</v>
-      </c>
-      <c r="I58" s="3">
-        <v>45717</v>
-      </c>
-      <c r="J58" s="3">
-        <v>47175</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>156</v>
-      </c>
-      <c r="B59" t="s">
-        <v>115</v>
-      </c>
-      <c r="C59" t="s">
-        <v>157</v>
-      </c>
-      <c r="D59" t="s">
-        <v>158</v>
-      </c>
-      <c r="E59" t="s">
-        <v>118</v>
-      </c>
-      <c r="F59" t="s">
-        <v>1</v>
-      </c>
-      <c r="G59" t="s">
-        <v>17</v>
-      </c>
-      <c r="H59" t="s">
-        <v>160</v>
-      </c>
-      <c r="I59" s="3">
-        <v>45870</v>
-      </c>
-      <c r="J59" s="3">
-        <v>47176</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>161</v>
-      </c>
-      <c r="B60" t="s">
-        <v>115</v>
-      </c>
-      <c r="C60" t="s">
-        <v>162</v>
-      </c>
-      <c r="D60" t="s">
-        <v>163</v>
-      </c>
-      <c r="E60" t="s">
-        <v>118</v>
-      </c>
-      <c r="F60" t="s">
-        <v>1</v>
-      </c>
-      <c r="G60" t="s">
-        <v>119</v>
-      </c>
-      <c r="H60" t="s">
-        <v>164</v>
-      </c>
-      <c r="I60" s="3">
-        <v>45717</v>
-      </c>
-      <c r="J60" s="3">
-        <v>47177</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>161</v>
-      </c>
-      <c r="B61" t="s">
-        <v>115</v>
-      </c>
-      <c r="C61" t="s">
-        <v>162</v>
-      </c>
-      <c r="D61" t="s">
-        <v>163</v>
-      </c>
-      <c r="E61" t="s">
-        <v>118</v>
-      </c>
-      <c r="F61" t="s">
-        <v>1</v>
-      </c>
-      <c r="G61" t="s">
-        <v>17</v>
-      </c>
-      <c r="H61" t="s">
-        <v>165</v>
-      </c>
-      <c r="I61" s="3">
-        <v>45870</v>
-      </c>
-      <c r="J61" s="3">
-        <v>47178</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>161</v>
-      </c>
-      <c r="B62" t="s">
-        <v>115</v>
-      </c>
-      <c r="C62" t="s">
-        <v>162</v>
-      </c>
-      <c r="D62" t="s">
-        <v>163</v>
-      </c>
-      <c r="E62" t="s">
-        <v>118</v>
-      </c>
-      <c r="F62" t="s">
-        <v>1</v>
-      </c>
-      <c r="G62" t="s">
-        <v>17</v>
-      </c>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+    </row>
+    <row r="33" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+    </row>
+    <row r="34" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+    </row>
+    <row r="35" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+    </row>
+    <row r="36" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+    </row>
+    <row r="37" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+    </row>
+    <row r="38" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+    </row>
+    <row r="39" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+    </row>
+    <row r="40" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+    </row>
+    <row r="41" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+    </row>
+    <row r="42" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+    </row>
+    <row r="43" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+    </row>
+    <row r="44" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+    </row>
+    <row r="45" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+    </row>
+    <row r="46" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+    </row>
+    <row r="47" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+    </row>
+    <row r="48" spans="9:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+    </row>
+    <row r="49" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+    </row>
+    <row r="50" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
+    </row>
+    <row r="51" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I51" s="3"/>
+      <c r="J51" s="3"/>
+    </row>
+    <row r="52" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I52" s="3"/>
+      <c r="J52" s="3"/>
+    </row>
+    <row r="53" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
+    </row>
+    <row r="54" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I54" s="3"/>
+      <c r="J54" s="3"/>
+    </row>
+    <row r="55" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+    </row>
+    <row r="56" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I56" s="3"/>
+      <c r="J56" s="3"/>
+    </row>
+    <row r="57" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I57" s="3"/>
+      <c r="J57" s="3"/>
+    </row>
+    <row r="58" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I58" s="3"/>
+      <c r="J58" s="3"/>
+    </row>
+    <row r="59" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I59" s="3"/>
+      <c r="J59" s="3"/>
+    </row>
+    <row r="60" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I60" s="3"/>
+      <c r="J60" s="3"/>
+    </row>
+    <row r="61" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="I61" s="3"/>
+      <c r="J61" s="3"/>
+    </row>
+    <row r="62" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
       <c r="I62" s="3"/>
       <c r="J62" s="3"/>
     </row>
-    <row r="63" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>161</v>
-      </c>
-      <c r="B63" t="s">
-        <v>115</v>
-      </c>
-      <c r="C63" t="s">
-        <v>162</v>
-      </c>
-      <c r="D63" t="s">
-        <v>163</v>
-      </c>
-      <c r="E63" t="s">
-        <v>118</v>
-      </c>
-      <c r="F63" t="s">
-        <v>1</v>
-      </c>
-      <c r="G63" t="s">
-        <v>17</v>
-      </c>
+    <row r="63" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
       <c r="I63" s="3"/>
       <c r="J63" s="3"/>
     </row>
-    <row r="64" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="64" spans="8:10" ht="13.2" x14ac:dyDescent="0.25">
       <c r="H64" s="2"/>
     </row>
     <row r="65" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
@@ -5624,6 +4365,852 @@
     </row>
     <row r="1000" spans="8:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="H1000" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C131186F-0D96-466D-B990-5C4B7CC32FF1}">
+  <dimension ref="B5:K30"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="10" max="10" width="13.33203125" customWidth="1"/>
+    <col min="11" max="11" width="15.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="2:11" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" ht="66" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="6">
+        <v>43831</v>
+      </c>
+      <c r="K6" s="6">
+        <v>47484</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="6">
+        <v>43831</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="6">
+        <v>43862</v>
+      </c>
+      <c r="K8" s="6">
+        <v>47515</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" ht="66" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="6">
+        <v>43876</v>
+      </c>
+      <c r="K9" s="6">
+        <v>47529</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" s="6">
+        <v>43876</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="B11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J11" s="6">
+        <v>43881</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" ht="66" x14ac:dyDescent="0.25">
+      <c r="B12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J12" s="6">
+        <v>43891</v>
+      </c>
+      <c r="K12" s="6">
+        <v>47543</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J13" s="6">
+        <v>43891</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" ht="66" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J14" s="6">
+        <v>43941</v>
+      </c>
+      <c r="K14" s="6">
+        <v>47593</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J15" s="6">
+        <v>43941</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" ht="66" x14ac:dyDescent="0.25">
+      <c r="B16" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J16" s="6">
+        <v>43961</v>
+      </c>
+      <c r="K16" s="6">
+        <v>47613</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="B17" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J17" s="6">
+        <v>43961</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="B18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J18" s="6">
+        <v>43966</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" ht="66" x14ac:dyDescent="0.25">
+      <c r="B19" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J19" s="6">
+        <v>43997</v>
+      </c>
+      <c r="K19" s="6">
+        <v>47649</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" ht="66" x14ac:dyDescent="0.25">
+      <c r="B20" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J20" s="6">
+        <v>43997</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="B21" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="J21" s="6">
+        <v>44013</v>
+      </c>
+      <c r="K21" s="6">
+        <v>47665</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="B22" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="J22" s="6">
+        <v>44013</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" ht="66" x14ac:dyDescent="0.25">
+      <c r="B23" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="J23" s="6">
+        <v>44063</v>
+      </c>
+      <c r="K23" s="6">
+        <v>47715</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="B24" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J24" s="6">
+        <v>44063</v>
+      </c>
+      <c r="K24" s="6">
+        <v>47715</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="B25" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J25" s="6">
+        <v>44063</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" ht="66" x14ac:dyDescent="0.25">
+      <c r="B26" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="J26" s="6">
+        <v>44079</v>
+      </c>
+      <c r="K26" s="6">
+        <v>47731</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="B27" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J27" s="6">
+        <v>44079</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="B28" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="J28" s="6">
+        <v>44114</v>
+      </c>
+      <c r="K28" s="6">
+        <v>47766</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="J29" s="6">
+        <v>44114</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="B30" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J30" s="6">
+        <v>44119</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
